--- a/Documentation/DeliveryPlan_IdleReservations.xlsx
+++ b/Documentation/DeliveryPlan_IdleReservations.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filip\Desktop\OICAR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filip\Desktop\IdleReservations\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11D7651-C9BE-4DE1-A5CE-B38A78A0F943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47DA08FF-2D31-47ED-9827-F9A6A4E46F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{0C61915D-0620-41F9-B1D4-32B20F08D66A}"/>
   </bookViews>
@@ -82,15 +82,9 @@
     <t>PLANIRANJE SIGURNOSTI I ZAŠTITE PODATAKA,+</t>
   </si>
   <si>
-    <t>IZRADA RUTA ZA LOG-IN, DOHVAČANJE JELOVNIKA LOKACIJA I KONTAKATA,</t>
-  </si>
-  <si>
     <t>IZRADA WEB-APP SUČELJA ZA KORISNIKE,</t>
   </si>
   <si>
-    <t>IZRADA ODVOJENOG WEB-APP SUČELJA ZA ADMINISTRATORE,</t>
-  </si>
-  <si>
     <t>IZRADA PROJEKTNE DOKUMENTACIJE,</t>
   </si>
   <si>
@@ -104,6 +98,12 @@
   </si>
   <si>
     <t>Plan isporuke - OICAR Projekt - IdleReservations,</t>
+  </si>
+  <si>
+    <t>IZRADA RUTA ZA LOG-IN, DOHVAČANJE RESTORANA, LOKACIJA I KONTAKATA,</t>
+  </si>
+  <si>
+    <t>IZRADA ODVOJENOG SUČELJA ZA ADMINISTRATORE,</t>
   </si>
 </sst>
 </file>
@@ -996,7 +996,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
@@ -1061,7 +1061,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
@@ -1081,12 +1081,12 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
@@ -1136,12 +1136,12 @@
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
@@ -1156,7 +1156,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
@@ -1166,7 +1166,7 @@
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/DeliveryPlan_IdleReservations.xlsx
+++ b/Documentation/DeliveryPlan_IdleReservations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filip\Desktop\IdleReservations\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47DA08FF-2D31-47ED-9827-F9A6A4E46F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DC8A9A-EF9A-47E2-B04A-D6ADD3406800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{0C61915D-0620-41F9-B1D4-32B20F08D66A}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{0C61915D-0620-41F9-B1D4-32B20F08D66A}"/>
   </bookViews>
   <sheets>
     <sheet name="DeliveryPlan_IdleReservation" sheetId="1" r:id="rId1"/>
@@ -91,9 +91,6 @@
     <t>IZRADA KORISNIČKE DOKUMENTACIJE,</t>
   </si>
   <si>
-    <t>DEPLOYMENT RJEŠ ENJA NA SERVER/CLOUD,</t>
-  </si>
-  <si>
     <t>IZRADA ZAVRŠNE PREZENTACIJE ZA DIONIKE,</t>
   </si>
   <si>
@@ -104,6 +101,9 @@
   </si>
   <si>
     <t>IZRADA ODVOJENOG SUČELJA ZA ADMINISTRATORE,</t>
+  </si>
+  <si>
+    <t>AUTOMATIZACIJA INTEGRACIJSKIH TESTOVA,</t>
   </si>
 </sst>
 </file>
@@ -992,181 +992,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A2D4854-8779-491C-A698-4E5E48714D55}">
   <dimension ref="A1:A35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
